--- a/관심종목/미국배당주_관리표.xlsx
+++ b/관심종목/미국배당주_관리표.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="미국 배당주 관리표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'미국 배당주 관리표'!$A$4:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'미국 배당주 관리표'!$A$4:$K$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1383,55 +1383,59 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3,6,9,12월</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>US 뱅코프</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>USB</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>NYUSB</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2,5,8,11월</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>허쉬</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>HSY</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>NYHSY</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>SCHD X</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>유지</t>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>15년 내외</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>SCHD O</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>12 소비재 식품 음료와 중복</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>추가</t>
         </is>
       </c>
     </row>
@@ -1443,17 +1447,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>티 로 프라이스 그룹</t>
+          <t>US 뱅코프</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>NDTROW</t>
+          <t>NYUSB</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1463,22 +1467,22 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>배당귀족</t>
+          <t>–</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>38년</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>귀족38 | SCHD O</t>
+          <t>SCHD X</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
@@ -1496,17 +1500,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>라마 애드버타이징</t>
+          <t>티 로 프라이스 그룹</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>LAMR</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>NDLAMR</t>
+          <t>NDTROW</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1516,22 +1520,22 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>– (리츠)</t>
+          <t>배당귀족</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>38년</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>리츠</t>
+          <t>귀족38 | SCHD O</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
@@ -1549,17 +1553,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>메드트로닉</t>
+          <t>라마 애드버타이징</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LAMR</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>NYMDT</t>
+          <t>NDLAMR</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1569,12 +1573,12 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>배당귀족</t>
+          <t>– (리츠)</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>47년</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1584,7 +1588,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>귀족47 | SCHD X</t>
+          <t>리츠</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
@@ -1602,17 +1606,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>베스트 바이</t>
+          <t>메드트로닉</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>NYBBY</t>
+          <t>NYMDT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1622,22 +1626,22 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>배당귀족</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>25년 미만</t>
+          <t>47년</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>SCHD O</t>
+          <t>귀족47 | SCHD X</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr"/>
@@ -1655,17 +1659,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>제이피모간 체이스</t>
+          <t>베스트 바이</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>NYJPM</t>
+          <t>NYBBY</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1680,17 +1684,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2009년 삭감</t>
+          <t>25년 미만</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>SCHD X</t>
+          <t>SCHD O</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
@@ -1708,17 +1712,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>킴벌리 클라크</t>
+          <t>제이피모간 체이스</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>NDKMB</t>
+          <t>NYJPM</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1728,32 +1732,28 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>배당왕</t>
+          <t>–</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>52년</t>
+          <t>2009년 삭감</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>왕족52 | SCHD O</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>12 소비재 생활용품과 중복</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>추가</t>
+          <t>SCHD X</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>유지</t>
         </is>
       </c>
     </row>
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>오토매틱 데이터 프로세싱</t>
+          <t>킴벌리 클라크</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>NDADP</t>
+          <t>NDKMB</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>51년</t>
+          <t>52년</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>왕족51 | SCHD O</t>
+          <t>왕족52 | SCHD O</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>09 SW와 중복</t>
+          <t>12 소비재 생활용품과 중복</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1822,178 +1822,299 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
+          <t>오토매틱 데이터 프로세싱</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>NDADP</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>배당왕</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>51년</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>왕족51 | SCHD O</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>09 SW와 중복</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>3,6,9,12월</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
           <t>비치 프라퍼티스</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>VICI</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>NYVICI</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>– (리츠)</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>7년</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>리츠 | 카지노 부동산</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>2018년 상장</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>추가</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>3,6,9,12월</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>알트리아 그룹</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>NYMO</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>배당왕</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>57년</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>왕족57 | SCHD O | 배당성향 높음</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>배당성향 90%대, 담배 판매 감소 주의</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>매월</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>리얼티 인컴</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>NYO</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>매월</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>배당귀족 (리츠)</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>31년</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>귀족31 | 월배당 리츠</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J31" s="7" t="inlineStr">
         <is>
           <t>리츠는 SCHD 편입 대상 아님</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
         <is>
           <t>추가</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>매월</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>메인 스트리트 캐피털</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>MAIN</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>NYMAIN</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>매월 + 특별</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>– (BDC)</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>BDC | 월배당 + 특별배당</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>분기말 특별배당</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr">
+      <c r="K32" s="6" t="inlineStr">
         <is>
           <t>추가</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>제외: 유나이티드 테라퓨틱스(UTHR) — 배당을 주지 않는 종목이라 뺌</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>보류: 화이자(PFE) — 배당성향 200%대, 2026년 배당 동결, SCHD 미편입, 배당락 1·5·7·11월로 구간과 안 맞음</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K30"/>
+  <autoFilter ref="A4:K32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/관심종목/미국배당주_관리표.xlsx
+++ b/관심종목/미국배당주_관리표.xlsx
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>S&amp;P 글로벌</t>
+          <t>S P 글로벌</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">

--- a/관심종목/미국배당주_관리표.xlsx
+++ b/관심종목/미국배당주_관리표.xlsx
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>S P 글로벌</t>
+          <t>S&amp;P 글로벌</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
